--- a/research/traditional_assets/database/data/estonia/estonia_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_software_system_application.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,97 +588,115 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.009161290322580644</v>
+        <v>0.127286663260092</v>
       </c>
       <c r="H2">
-        <v>-0.009161290322580644</v>
+        <v>0.127286663260092</v>
       </c>
       <c r="I2">
-        <v>-0.07509677419354838</v>
+        <v>0.1008686765457333</v>
       </c>
       <c r="J2">
-        <v>-0.07509677419354838</v>
+        <v>0.1007566002384602</v>
       </c>
       <c r="K2">
-        <v>-0.677</v>
+        <v>1.645</v>
       </c>
       <c r="L2">
-        <v>-0.08735483870967743</v>
+        <v>0.08405723045477771</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.05303319343761922</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>1.689969604863222</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.05303319343761922</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>1.689969604863222</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>9.27</v>
+        <v>7.384</v>
       </c>
       <c r="V2">
-        <v>0.1267952400492409</v>
+        <v>0.1408622663105685</v>
+      </c>
+      <c r="W2">
+        <v>-0.04756637168141593</v>
       </c>
       <c r="X2">
-        <v>0.1372179439572472</v>
+        <v>0.1107832977893087</v>
+      </c>
+      <c r="Y2">
+        <v>-0.1583496694707247</v>
+      </c>
+      <c r="Z2">
+        <v>0.3479605988407241</v>
+      </c>
+      <c r="AA2">
+        <v>-0.05025868440502587</v>
       </c>
       <c r="AB2">
-        <v>0.1327033315909105</v>
+        <v>0.1107832977893087</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1602447835775871</v>
       </c>
       <c r="AD2">
-        <v>0.909</v>
+        <v>0.777</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.909</v>
+        <v>0.777</v>
       </c>
       <c r="AG2">
-        <v>-8.360999999999999</v>
+        <v>-6.607</v>
       </c>
       <c r="AH2">
-        <v>0.01228063064888745</v>
+        <v>0.01460608680940655</v>
       </c>
       <c r="AI2">
-        <v>0.01382951208751084</v>
+        <v>0.01101237297504146</v>
       </c>
       <c r="AJ2">
-        <v>-0.1291294074039754</v>
+        <v>-0.1442167070482178</v>
       </c>
       <c r="AK2">
-        <v>-0.1480897642537062</v>
+        <v>-0.1045858198914093</v>
       </c>
       <c r="AL2">
-        <v>0.053</v>
+        <v>0.049</v>
       </c>
       <c r="AM2">
-        <v>0.053</v>
+        <v>0.031</v>
       </c>
       <c r="AN2">
-        <v>-1.980392156862745</v>
+        <v>0.3232113144758736</v>
       </c>
       <c r="AO2">
-        <v>-10.9811320754717</v>
+        <v>40.28571428571428</v>
       </c>
       <c r="AP2">
-        <v>18.2156862745098</v>
+        <v>-2.748336106489185</v>
       </c>
       <c r="AQ2">
-        <v>-10.9811320754717</v>
+        <v>63.67741935483871</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AS Modera (TLSE:MODE)</t>
+          <t>TextMagic AS (TLSE:MAGIC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -698,97 +716,112 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.03534136546184739</v>
+        <v>0.2243589743589744</v>
       </c>
       <c r="H3">
-        <v>-0.03534136546184739</v>
+        <v>0.2243589743589744</v>
       </c>
       <c r="I3">
-        <v>-0.1927710843373494</v>
+        <v>0.1737179487179487</v>
       </c>
       <c r="J3">
-        <v>-0.1927710843373494</v>
+        <v>0.1731388888888889</v>
       </c>
       <c r="K3">
-        <v>-0.517</v>
+        <v>2.4</v>
       </c>
       <c r="L3">
-        <v>-0.2076305220883534</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.78</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.07037974683544303</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.158333333333333</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>2.78</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07037974683544303</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.158333333333333</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>1.37</v>
+        <v>6.08</v>
       </c>
       <c r="V3">
-        <v>0.1731984829329962</v>
+        <v>0.1539240506329114</v>
+      </c>
+      <c r="W3">
+        <v>0.03980099502487562</v>
       </c>
       <c r="X3">
-        <v>0.1415431185393946</v>
+        <v>0.1107832977893087</v>
+      </c>
+      <c r="Y3">
+        <v>-0.07098230276443308</v>
+      </c>
+      <c r="Z3">
+        <v>0.2989479332349615</v>
+      </c>
+      <c r="AA3">
+        <v>0.05175951299593098</v>
       </c>
       <c r="AB3">
-        <v>0.1325138938067212</v>
+        <v>0.1107832977893087</v>
+      </c>
+      <c r="AC3">
+        <v>-0.05902378479337772</v>
       </c>
       <c r="AD3">
-        <v>0.909</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.909</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.4610000000000001</v>
+        <v>-6.08</v>
       </c>
       <c r="AH3">
-        <v>0.1030729107608572</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.1674341499355314</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.06188750167807761</v>
+        <v>-0.1819269898264512</v>
       </c>
       <c r="AK3">
-        <v>-0.1135747721113575</v>
+        <v>-0.1066292528937215</v>
       </c>
       <c r="AL3">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.053</v>
+        <v>-0.017</v>
       </c>
       <c r="AN3">
-        <v>-1.909663865546219</v>
-      </c>
-      <c r="AO3">
-        <v>-9.056603773584905</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.9684873949579834</v>
+        <v>-1.961290322580645</v>
       </c>
       <c r="AQ3">
-        <v>-9.056603773584905</v>
+        <v>-159.4117647058823</v>
       </c>
     </row>
     <row r="4">
@@ -799,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TextMagic AS (TLSE:MAGIC)</t>
+          <t>AS Modera (TLSE:MODE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -808,22 +841,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.003231939163498099</v>
+        <v>-0.147979797979798</v>
       </c>
       <c r="H4">
-        <v>0.003231939163498099</v>
+        <v>-0.147979797979798</v>
       </c>
       <c r="I4">
-        <v>-0.01939163498098859</v>
+        <v>-0.05151515151515151</v>
       </c>
       <c r="J4">
-        <v>-0.01939163498098859</v>
+        <v>-0.05151515151515151</v>
       </c>
       <c r="K4">
-        <v>-0.16</v>
+        <v>-0.215</v>
       </c>
       <c r="L4">
-        <v>-0.03041825095057035</v>
+        <v>-0.0542929292929293</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -847,52 +880,183 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>7.9</v>
+        <v>0.998</v>
       </c>
       <c r="V4">
-        <v>0.1211656441717791</v>
+        <v>0.1002008032128514</v>
+      </c>
+      <c r="W4">
+        <v>-0.04756637168141593</v>
       </c>
       <c r="X4">
-        <v>0.1328927693750998</v>
+        <v>0.11527574938628</v>
+      </c>
+      <c r="Y4">
+        <v>-0.162842121067696</v>
+      </c>
+      <c r="Z4">
+        <v>0.9756097560975612</v>
+      </c>
+      <c r="AA4">
+        <v>-0.05025868440502587</v>
       </c>
       <c r="AB4">
-        <v>0.1328927693750998</v>
+        <v>0.1099860991725612</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1602447835775871</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="AG4">
-        <v>-7.9</v>
+        <v>-0.221</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.07236658284436993</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.1230014247269273</v>
       </c>
       <c r="AJ4">
-        <v>-0.137870855148342</v>
+        <v>-0.02269226820002053</v>
       </c>
       <c r="AK4">
-        <v>-0.150763358778626</v>
+        <v>-0.04154916337657454</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>-3.924242424242424</v>
+      </c>
+      <c r="AO4">
+        <v>-4.533333333333333</v>
       </c>
       <c r="AP4">
-        <v>-464.7058823529412</v>
+        <v>1.116161616161616</v>
+      </c>
+      <c r="AQ4">
+        <v>-4.636363636363637</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Grab2Go AS (TLSE:GRB2G)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Software (System &amp; Application)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-42.3</v>
+      </c>
+      <c r="H5">
+        <v>-42.3</v>
+      </c>
+      <c r="I5">
+        <v>-53.2</v>
+      </c>
+      <c r="J5">
+        <v>-53.2</v>
+      </c>
+      <c r="K5">
+        <v>-0.54</v>
+      </c>
+      <c r="L5">
+        <v>-54</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.306</v>
+      </c>
+      <c r="V5">
+        <v>0.1033783783783784</v>
+      </c>
+      <c r="X5">
+        <v>0.1107832977893087</v>
+      </c>
+      <c r="AB5">
+        <v>0.1107832977893087</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-0.306</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.1152976639035418</v>
+      </c>
+      <c r="AK5">
+        <v>-0.3669064748201439</v>
+      </c>
+      <c r="AL5">
+        <v>0.004</v>
+      </c>
+      <c r="AM5">
+        <v>0.004</v>
+      </c>
+      <c r="AN5">
+        <v>-0</v>
+      </c>
+      <c r="AO5">
+        <v>-133</v>
+      </c>
+      <c r="AP5">
+        <v>0.6144578313253012</v>
+      </c>
+      <c r="AQ5">
+        <v>-133</v>
       </c>
     </row>
   </sheetData>
